--- a/tests/fixtures/image/image-basic-sample02.xlsx
+++ b/tests/fixtures/image/image-basic-sample02.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/igapyon/Documents/git/local-html-tools/docs/xlsx2md/tests/fixtures/image/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC277FCF-4DB8-B942-AD0B-2054E5ED345E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1200" yWindow="600" windowWidth="27340" windowHeight="16760" xr2:uid="{95EFFC77-0BB9-C24C-8C40-5FB8F9D33BDC}"/>
